--- a/SGC-CKN/Excel/23ffa9f6-df42-48f7-932b-f37bd78c67d0_Lô_CT-02_P7-131_D800_08-03-2026.xlsx
+++ b/SGC-CKN/Excel/23ffa9f6-df42-48f7-932b-f37bd78c67d0_Lô_CT-02_P7-131_D800_08-03-2026.xlsx
@@ -135,7 +135,7 @@
     <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
-    <t xml:space="preserve">14:30
+    <t xml:space="preserve">14:39
 08/03/2026</t>
   </si>
   <si>
@@ -1293,13 +1293,13 @@
         <v>-21</v>
       </c>
       <c r="H14" s="16">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="I14" s="16">
         <v>4.3</v>
       </c>
       <c r="J14" s="12">
-        <v>2.87</v>
+        <v>2.61</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
@@ -1722,13 +1722,13 @@
         <v>-21</v>
       </c>
       <c r="G5" s="16">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="H5" s="16">
         <v>4.3</v>
       </c>
       <c r="I5" s="12">
-        <v>2.87</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1896,13 +1896,13 @@
         <v>-45.2</v>
       </c>
       <c r="G11" s="36">
-        <v>7.78</v>
+        <v>7.93</v>
       </c>
       <c r="H11" s="36">
         <v>44.01</v>
       </c>
       <c r="I11" s="36">
-        <v>5.65</v>
+        <v>5.55</v>
       </c>
     </row>
   </sheetData>
